--- a/examples/medibec/deliverables/MediBec_CyberRiskGuardian_Workbook_30_Budget.xlsx
+++ b/examples/medibec/deliverables/MediBec_CyberRiskGuardian_Workbook_30_Budget.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
@@ -299,7 +299,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Opportunistic; depends on telehealth volume (Evidence gap). Evidence: E2</t>
+          <t xml:space="preserve">Opportunistic; depends on telehealth volume (Information gap). Evidence: E2</t>
         </r>
       </text>
     </comment>
@@ -2219,7 +2219,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Representative weakness: malicious macro document leading to code execution (initial vector in E6). AV:N delivered by e-mail; AC:L; AT:N; PR:N; UI:P user opens the document; VC/VI/VA:H on the workstation; SC/SI/SA:H because EHR and clinic systems are subsequently affected. CVSS describes the entry weakness only, not the enterprise impact.</t>
+          <t xml:space="preserve">Representative weakness: malicious macro document leading to code execution (initial vector in E6). AV:L: the document is delivered by e-mail but opened and executed locally on the workstation (FIRST CVSS v4.0 user guide scores malicious documents as Local whatever the delivery channel); AC:L; AT:N; PR:N; UI:P user opens the document; VC/VI/VA:H on the workstation; SC/SI/SA:H because EHR and clinic systems are subsequently affected. CVSS describes the entry weakness only, not the enterprise impa</t>
         </r>
       </text>
     </comment>
@@ -2291,7 +2291,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Limited applicability: a detection gap is a control weakness, not a vulnerability. Representative weakness for the workbook: the undetected initial code-execution vector (macro/PowerShell, E6). Do not interpret the score as the severity of the detection gap.</t>
+          <t xml:space="preserve">Limited applicability: a detection gap is a control weakness, not a vulnerability. Representative weakness for the workbook: the undetected initial code-execution vector (macro/PowerShell, E6), scored AV:L because the e-mailed document is opened and executed locally (FIRST CVSS v4.0 user guide). Do not interpret the score as the severity of the detection gap.</t>
         </r>
       </text>
     </comment>
@@ -2575,7 +2575,7 @@
     <t xml:space="preserve">30-scenario assessment (S1-S10 carried over unchanged from the 10-scenario assessment; S11-S30 added). Source: MediBec Business Case v2.0b (fictional teaching case, M.-A. Leger) and CyberRiskGuardian Excel Guide v1.0c formulas.</t>
   </si>
   <si>
-    <t xml:space="preserve">All parameter values, CVSS vectors, costs and reductions are ANALYST ESTIMATES - VALIDATION REQUIRED. Scores are relative decision-support indicators, not loss predictions.</t>
+    <t xml:space="preserve">All parameter values, CVSS vectors, costs and reductions are analytical estimates (Analytical estimate — validation required). Scores are relative decision-support indicators, not loss predictions.</t>
   </si>
   <si>
     <t xml:space="preserve">Colour legend:  blue text = input you may edit  |  black = formula  |  green = link to another sheet  |  yellow fill = key assumption.</t>
@@ -2641,7 +2641,7 @@
     <t xml:space="preserve">  Budget_Risk    - residual risk and tolerance status at portfolio vs. second-wave funding.</t>
   </si>
   <si>
-    <t xml:space="preserve">Analyse - CyberRiskGuardian KRIs (Excel Guide v1.0c formulas)</t>
+    <t xml:space="preserve">Analyse - CyberRiskGuardian risk indices (Excel Guide v1.0c formulas)</t>
   </si>
   <si>
     <t xml:space="preserve">Green = linked from Inputs / Portfolio / Parameters; black = formula.</t>
@@ -2734,10 +2734,10 @@
     <t xml:space="preserve">Source / note</t>
   </si>
   <si>
-    <t xml:space="preserve">Risk appetite (analyst estimate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analyst estimate - validation required. Case states 0.40 normalized tolerance; see report s.4.</t>
+    <t xml:space="preserve">Risk appetite (analytical estimate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytical estimate — validation required. Case states 0.40 normalized tolerance; see report s.4.</t>
   </si>
   <si>
     <t xml:space="preserve">Multiplication factor</t>
@@ -2776,7 +2776,7 @@
     <t xml:space="preserve">Case escalation - Board acceptance threshold</t>
   </si>
   <si>
-    <t xml:space="preserve">Scenario inputs (0-1 scale unless stated) - Analyst estimates, validation required</t>
+    <t xml:space="preserve">Scenario inputs (0-1 scale unless stated) - Analytical estimate — validation required</t>
   </si>
   <si>
     <t xml:space="preserve">CVSS v4.0 vector</t>
@@ -2824,7 +2824,7 @@
     <t xml:space="preserve">Ransomware disrupting EHR access and clinic operations across the network</t>
   </si>
   <si>
-    <t xml:space="preserve">CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:P/VC:H/VI:H/VA:H/SC:H/SI:H/SA:H</t>
+    <t xml:space="preserve">CVSS:4.0/AV:L/AC:L/AT:N/PR:N/UI:P/VC:H/VI:H/VA:H/SC:H/SI:H/SA:H</t>
   </si>
   <si>
     <t xml:space="preserve">S3</t>
@@ -2878,7 +2878,7 @@
     <t xml:space="preserve">Detection and response gaps allow an intrusion to persist and escalate</t>
   </si>
   <si>
-    <t xml:space="preserve">CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:P/VC:H/VI:H/VA:L/SC:H/SI:L/SA:L</t>
+    <t xml:space="preserve">CVSS:4.0/AV:L/AC:L/AT:N/PR:N/UI:P/VC:H/VI:H/VA:L/SC:H/SI:L/SA:L</t>
   </si>
   <si>
     <t xml:space="preserve">S9</t>
@@ -3460,7 +3460,7 @@
     <t xml:space="preserve">Allocation assumption: each initiative's Year-1 cost is split equally across the scenarios it addresses, so shared controls are never charged in full to several scenarios.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cyber-insurance premium is excluded (Evidence gap - broker quotation required).</t>
+    <t xml:space="preserve">Cyber-insurance premium is excluded (Information gap — organizational validation required: broker quotation required).</t>
   </si>
   <si>
     <t xml:space="preserve">Sensitivity - lower / central / higher cases</t>
@@ -3586,7 +3586,7 @@
     <t xml:space="preserve">Cybercriminal (initial-access broker or ransomware affiliate).</t>
   </si>
   <si>
-    <t xml:space="preserve">Push-based MFA without number matching or phishing resistance (E6 - validate); No evidence of conditional access (geo/device) policies; Internet-sourced macro documents reach users (E6); Awareness programme maturity unknown (Evidence gap)</t>
+    <t xml:space="preserve">Push-based MFA without number matching or phishing resistance (E6 - validate); No evidence of conditional access (geo/device) policies; Internet-sourced macro documents reach users (E6); Awareness programme maturity unknown (Information gap)</t>
   </si>
   <si>
     <t xml:space="preserve">Email filtering / antimalware (E2 - effectiveness unknown); MFA push on remote access (E6); EDR alerting (E6 - triage weak)</t>
@@ -3613,7 +3613,7 @@
     <t xml:space="preserve">Ransomware-as-a-service affiliate (double extortion).</t>
   </si>
   <si>
-    <t xml:space="preserve">Macro execution and weak alert triage (E6); Segmentation between clinics, servers and backups not evidenced (E2, E7); Privileged credential hygiene unknown (Evidence gap); Clinic downtime procedures untested (E7)</t>
+    <t xml:space="preserve">Macro execution and weak alert triage (E6); Segmentation between clinics, servers and backups not evidenced (E2, E7); Privileged credential hygiene unknown (Information gap); Clinic downtime procedures untested (E7)</t>
   </si>
   <si>
     <t xml:space="preserve">Firewalls, IDS/IPS, antimalware (E2); EDR (E6); On-site and off-site backups (E2 - isolation and testing unknown); Incident command structure defined (E6 - untested)</t>
@@ -3631,7 +3631,7 @@
     <t xml:space="preserve">0-24 months</t>
   </si>
   <si>
-    <t xml:space="preserve">Representative weakness: malicious macro document leading to code execution (initial vector in E6). AV:N delivered by e-mail; AC:L; AT:N; PR:N; UI:P user opens the document; VC/VI/VA:H on the workstation; SC/SI/SA:H because EHR and clinic systems are subsequently affected. CVSS describes the entry weakness only, not the enterprise impact.</t>
+    <t xml:space="preserve">Representative weakness: malicious macro document leading to code execution (initial vector in E6). AV:L: the document is delivered by e-mail but opened and executed locally on the workstation (FIRST CVSS v4.0 user guide scores malicious documents as Local whatever the delivery channel); AC:L; AT:N; PR:N; UI:P user opens the document; VC/VI/VA:H on the workstation; SC/SI/SA:H because EHR and clinic systems are subsequently affected. CVSS describes the entry weakness only, not the enterprise impact.</t>
   </si>
   <si>
     <t xml:space="preserve">MED-CYR-07</t>
@@ -3727,7 +3727,7 @@
     <t xml:space="preserve">Cybercriminal / state-linked actor using public exploits.</t>
   </si>
   <si>
-    <t xml:space="preserve">Patch SLAs and exception governance not evidenced (E7); Incomplete asset inventory (E4); Possible end-of-life systems (Evidence gap)</t>
+    <t xml:space="preserve">Patch SLAs and exception governance not evidenced (E7); Incomplete asset inventory (E4); Possible end-of-life systems (Information gap)</t>
   </si>
   <si>
     <t xml:space="preserve">Firewalls, IDS/IPS (E2); Antimalware (E2)</t>
@@ -3796,7 +3796,7 @@
     <t xml:space="preserve">I01, I03, I11, I12</t>
   </si>
   <si>
-    <t xml:space="preserve">Limited applicability: a detection gap is a control weakness, not a vulnerability. Representative weakness for the workbook: the undetected initial code-execution vector (macro/PowerShell, E6). Do not interpret the score as the severity of the detection gap.</t>
+    <t xml:space="preserve">Limited applicability: a detection gap is a control weakness, not a vulnerability. Representative weakness for the workbook: the undetected initial code-execution vector (macro/PowerShell, E6), scored AV:L because the e-mailed document is opened and executed locally (FIRST CVSS v4.0 user guide). Do not interpret the score as the severity of the detection gap.</t>
   </si>
   <si>
     <t xml:space="preserve">MED-CYR-14</t>
@@ -3868,7 +3868,7 @@
     <t xml:space="preserve">Opportunistic actor scanning public repositories and paste sites; cybercriminal.</t>
   </si>
   <si>
-    <t xml:space="preserve">No secret scanning or vault evidenced (E7); Long-lived API keys without rotation (Analyst assumption); API calls not monitored for anomalous volume (E7); Development practices and repository visibility unknown (Evidence gap)</t>
+    <t xml:space="preserve">No secret scanning or vault evidenced (E7); Long-lived API keys without rotation (Analyst assumption); API calls not monitored for anomalous volume (E7); Development practices and repository visibility unknown (Information gap)</t>
   </si>
   <si>
     <t xml:space="preserve">Encrypted storage (E2 - does not protect against valid-key access)</t>
@@ -3895,7 +3895,7 @@
     <t xml:space="preserve">Local attacker (visitor, patient, passer-by) or opportunistic cybercriminal.</t>
   </si>
   <si>
-    <t xml:space="preserve">Guest and clinical Wi-Fi segmentation not evidenced (E7); Wireless standard and key management unknown (Evidence gap); No rogue AP detection evidenced; Flat clinic LAN (Analyst assumption, see S7)</t>
+    <t xml:space="preserve">Guest and clinical Wi-Fi segmentation not evidenced (E7); Wireless standard and key management unknown (Information gap); No rogue AP detection evidenced; Flat clinic LAN (Analyst assumption, see S7)</t>
   </si>
   <si>
     <t xml:space="preserve">Firewalls and IDS/IPS at the Montreal hub (E2 - clinic-level coverage unknown)</t>
@@ -6082,7 +6082,7 @@
     <t xml:space="preserve">Methodology</t>
   </si>
   <si>
-    <t xml:space="preserve">Authoritative KRI formulas; CVSS v4.0; multiplication factor 1,000 in worked example; reductions must stay within 0-1.</t>
+    <t xml:space="preserve">Authoritative risk-index formulas; CVSS v4.0; multiplication factor 1,000 in worked example; reductions must stay within 0-1.</t>
   </si>
   <si>
     <t xml:space="preserve">E11</t>
@@ -6112,7 +6112,7 @@
     <t xml:space="preserve">Total IT budget incl. salaries (CAD)</t>
   </si>
   <si>
-    <t xml:space="preserve">Business case s.4 (E3). Evidence gap - appears high for a 15-person IT team; validate with Finance.</t>
+    <t xml:space="preserve">Business case s.4 (E3). Information gap — organizational validation required: appears high for a 15-person IT team; validate with Finance.</t>
   </si>
   <si>
     <t xml:space="preserve">Guideline floor - risk seeking (% of IT budget)</t>
@@ -6130,7 +6130,7 @@
     <t xml:space="preserve">Risk appetite (linked)</t>
   </si>
   <si>
-    <t xml:space="preserve">From Parameters sheet (analyst estimate 0.30).</t>
+    <t xml:space="preserve">From Parameters sheet (analytical estimate 0.30).</t>
   </si>
   <si>
     <t xml:space="preserve">Appetite anchor for ceiling (risk averse)</t>
@@ -6589,7 +6589,7 @@
     <t xml:space="preserve">Cybersecurity run (operating) budget</t>
   </si>
   <si>
-    <t xml:space="preserve">Sensitivity to the IT budget figure (evidence gap) - option D and recommended</t>
+    <t xml:space="preserve">Sensitivity to the IT budget figure (information gap) - option D and recommended</t>
   </si>
   <si>
     <t xml:space="preserve">IT budget (CAD)</t>
@@ -6610,7 +6610,7 @@
     <t xml:space="preserve">Target CAD @ appetite</t>
   </si>
   <si>
-    <t xml:space="preserve">Residual risk by funding level (same CRG formulas; second-wave reductions are analyst estimates)</t>
+    <t xml:space="preserve">Residual risk by funding level (same CRG formulas; second-wave reductions are analytical estimates)</t>
   </si>
   <si>
     <t xml:space="preserve">P (portfolio)</t>
@@ -8497,7 +8497,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
         <v>1181</v>
       </c>
@@ -11932,7 +11932,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="38" t="n">
-        <v>800000.000000001</v>
+        <v>800000</v>
       </c>
       <c r="H64" s="38" t="n">
         <v>400000</v>
@@ -11955,7 +11955,7 @@
       </c>
       <c r="M64" s="43" t="n">
         <f aca="false">G64*(1-$E64)</f>
-        <v>640000.000000001</v>
+        <v>640000</v>
       </c>
       <c r="N64" s="43" t="n">
         <f aca="false">H64*(1-$E64)</f>
@@ -13716,11 +13716,11 @@
       </c>
       <c r="C5" s="47" t="n">
         <f aca="false">Analyse!L6</f>
-        <v>7893.48214285714</v>
+        <v>7809.50892857143</v>
       </c>
       <c r="D5" s="47" t="n">
         <f aca="false">Analyse!M6</f>
-        <v>2870.35714285714</v>
+        <v>2839.82142857143</v>
       </c>
       <c r="E5" s="35" t="n">
         <f aca="false">Inputs!K5</f>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="G5" s="48" t="n">
         <f aca="false">C5*(1-E5*F5)</f>
-        <v>3453.3984375</v>
+        <v>3416.66015625</v>
       </c>
       <c r="H5" s="44" t="n">
         <f aca="false">G5/D5</f>
@@ -13750,11 +13750,11 @@
       </c>
       <c r="L5" s="48" t="n">
         <f aca="false">C5*(1-J5*K5)</f>
-        <v>2841.65357142857</v>
+        <v>2811.42321428571</v>
       </c>
       <c r="M5" s="44" t="n">
         <f aca="false">L5/D5</f>
-        <v>0.99</v>
+        <v>0.989999999999999</v>
       </c>
       <c r="N5" s="32" t="str">
         <f aca="false">IF(M5&lt;Parameters!$B$6,"Below tolerance",IF(M5&lt;=Parameters!$B$7,"Approximately at tolerance","Above tolerance"))</f>
@@ -14052,11 +14052,11 @@
       </c>
       <c r="C11" s="47" t="n">
         <f aca="false">Analyse!L12</f>
-        <v>9486</v>
+        <v>9384</v>
       </c>
       <c r="D11" s="47" t="n">
         <f aca="false">Analyse!M12</f>
-        <v>3794.4</v>
+        <v>3753.6</v>
       </c>
       <c r="E11" s="35" t="n">
         <f aca="false">Inputs!K11</f>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="G11" s="48" t="n">
         <f aca="false">C11*(1-E11*F11)</f>
-        <v>4173.84</v>
+        <v>4128.96</v>
       </c>
       <c r="H11" s="44" t="n">
         <f aca="false">G11/D11</f>
@@ -14086,7 +14086,7 @@
       </c>
       <c r="L11" s="48" t="n">
         <f aca="false">C11*(1-J11*K11)</f>
-        <v>3794.4</v>
+        <v>3753.6</v>
       </c>
       <c r="M11" s="44" t="n">
         <f aca="false">L11/D11</f>
@@ -15374,11 +15374,11 @@
       </c>
       <c r="C38" s="48" t="n">
         <f aca="false">SUM(G4:G33)</f>
-        <v>41104.3861752232</v>
+        <v>41022.7678939732</v>
       </c>
       <c r="D38" s="48" t="n">
         <f aca="false">SUM(L4:L33)</f>
-        <v>34136.7923616071</v>
+        <v>34065.7620044643</v>
       </c>
     </row>
   </sheetData>
@@ -15637,7 +15637,7 @@
       </c>
       <c r="E6" s="9" t="n">
         <f aca="false">Inputs!J5</f>
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="F6" s="8" t="n">
         <f aca="false">Inputs!E5</f>
@@ -15665,11 +15665,11 @@
       </c>
       <c r="L6" s="11" t="n">
         <f aca="false">C6*D6*E6*((F6+G6)/2)*H6/I6*K6</f>
-        <v>7893.48214285714</v>
+        <v>7809.50892857143</v>
       </c>
       <c r="M6" s="11" t="n">
         <f aca="false">C6*D6*E6*J6*H6/I6*K6</f>
-        <v>2870.35714285714</v>
+        <v>2839.82142857143</v>
       </c>
       <c r="N6" s="12" t="n">
         <f aca="false">L6/M6</f>
@@ -15689,11 +15689,11 @@
       </c>
       <c r="R6" s="11" t="n">
         <f aca="false">L6*P6*Q6</f>
-        <v>4440.08370535714</v>
+        <v>4392.84877232143</v>
       </c>
       <c r="S6" s="11" t="n">
         <f aca="false">L6-R6</f>
-        <v>3453.3984375</v>
+        <v>3416.66015625</v>
       </c>
       <c r="T6" s="12" t="n">
         <f aca="false">S6/M6</f>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="V6" s="12" t="n">
         <f aca="false">IF(O6=0,0,(L6-S6)/O6*1000)</f>
-        <v>12.4600634788693</v>
+        <v>12.3275096120728</v>
       </c>
       <c r="W6" s="14" t="str">
         <f aca="false">IF(AND(P6&gt;=0,P6&lt;=1,Q6&gt;=0,Q6&lt;=1),"OK","CHECK")</f>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="E12" s="9" t="n">
         <f aca="false">Inputs!J11</f>
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="F12" s="8" t="n">
         <f aca="false">Inputs!E11</f>
@@ -16229,11 +16229,11 @@
       </c>
       <c r="L12" s="11" t="n">
         <f aca="false">C12*D12*E12*((F12+G12)/2)*H12/I12*K12</f>
-        <v>9486</v>
+        <v>9384</v>
       </c>
       <c r="M12" s="11" t="n">
         <f aca="false">C12*D12*E12*J12*H12/I12*K12</f>
-        <v>3794.4</v>
+        <v>3753.6</v>
       </c>
       <c r="N12" s="12" t="n">
         <f aca="false">L12/M12</f>
@@ -16253,11 +16253,11 @@
       </c>
       <c r="R12" s="11" t="n">
         <f aca="false">L12*P12*Q12</f>
-        <v>5312.16</v>
+        <v>5255.04</v>
       </c>
       <c r="S12" s="11" t="n">
         <f aca="false">L12-R12</f>
-        <v>4173.84</v>
+        <v>4128.96</v>
       </c>
       <c r="T12" s="12" t="n">
         <f aca="false">S12/M12</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="V12" s="12" t="n">
         <f aca="false">IF(O12=0,0,(L12-S12)/O12*1000)</f>
-        <v>48.7450166215429</v>
+        <v>48.2208766578704</v>
       </c>
       <c r="W12" s="14" t="str">
         <f aca="false">IF(AND(P12&gt;=0,P12&lt;=1,Q12&gt;=0,Q12&lt;=1),"OK","CHECK")</f>
@@ -18350,11 +18350,11 @@
       </c>
       <c r="L35" s="16" t="n">
         <f aca="false">SUM(L5:L34)</f>
-        <v>84491.4444196429</v>
+        <v>84305.4712053571</v>
       </c>
       <c r="M35" s="16" t="n">
         <f aca="false">SUM(M5:M34)</f>
-        <v>37194.5928571429</v>
+        <v>37123.2571428571</v>
       </c>
       <c r="O35" s="17" t="n">
         <f aca="false">SUM(O5:O34)</f>
@@ -18362,19 +18362,19 @@
       </c>
       <c r="R35" s="16" t="n">
         <f aca="false">SUM(R5:R34)</f>
-        <v>43387.0582444197</v>
+        <v>43282.7033113839</v>
       </c>
       <c r="S35" s="16" t="n">
         <f aca="false">SUM(S5:S34)</f>
-        <v>41104.3861752232</v>
+        <v>41022.7678939732</v>
       </c>
       <c r="T35" s="18" t="n">
         <f aca="false">S35/M35</f>
-        <v>1.1051172500556</v>
+        <v>1.10504225790614</v>
       </c>
       <c r="V35" s="18" t="n">
         <f aca="false">(L35-S35)/O35*1000</f>
-        <v>8.16928229041982</v>
+        <v>8.14963346100243</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18700,7 +18700,7 @@
         <v>86</v>
       </c>
       <c r="J5" s="23" t="n">
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="K5" s="22" t="n">
         <v>0.75</v>
@@ -19036,7 +19036,7 @@
         <v>104</v>
       </c>
       <c r="J11" s="23" t="n">
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="K11" s="22" t="n">
         <v>0.7</v>
@@ -23831,7 +23831,7 @@
       </c>
       <c r="J5" s="9" t="n">
         <f aca="false">Inputs!J5</f>
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="K5" s="12" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K5-C5))</f>
@@ -23843,15 +23843,15 @@
       </c>
       <c r="M5" s="11" t="n">
         <f aca="false">D5*E5*J5*((F5+G5)/2)*I5/H5*Parameters!$B$5</f>
-        <v>3740.67777777778</v>
+        <v>3700.88333333333</v>
       </c>
       <c r="N5" s="11" t="n">
         <f aca="false">D5*E5*J5*Parameters!$B$4*I5/H5*Parameters!$B$5</f>
-        <v>1547.86666666667</v>
+        <v>1531.4</v>
       </c>
       <c r="O5" s="11" t="n">
         <f aca="false">M5-M5*K5*L5</f>
-        <v>1038.03808333333</v>
+        <v>1026.995125</v>
       </c>
       <c r="P5" s="12" t="n">
         <f aca="false">O5/N5</f>
@@ -23899,7 +23899,7 @@
       </c>
       <c r="J6" s="9" t="n">
         <f aca="false">Inputs!J5</f>
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="K6" s="12" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K5-C6))</f>
@@ -23911,15 +23911,15 @@
       </c>
       <c r="M6" s="11" t="n">
         <f aca="false">D6*E6*J6*((F6+G6)/2)*I6/H6*Parameters!$B$5</f>
-        <v>7893.48214285714</v>
+        <v>7809.50892857143</v>
       </c>
       <c r="N6" s="11" t="n">
         <f aca="false">D6*E6*J6*Parameters!$B$4*I6/H6*Parameters!$B$5</f>
-        <v>2870.35714285714</v>
+        <v>2839.82142857143</v>
       </c>
       <c r="O6" s="11" t="n">
         <f aca="false">M6-M6*K6*L6</f>
-        <v>3453.3984375</v>
+        <v>3416.66015625</v>
       </c>
       <c r="P6" s="12" t="n">
         <f aca="false">O6/N6</f>
@@ -23967,7 +23967,7 @@
       </c>
       <c r="J7" s="9" t="n">
         <f aca="false">Inputs!J5</f>
-        <v>9.4</v>
+        <v>9.3</v>
       </c>
       <c r="K7" s="12" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K5-C7))</f>
@@ -23979,15 +23979,15 @@
       </c>
       <c r="M7" s="11" t="n">
         <f aca="false">D7*E7*J7*((F7+G7)/2)*I7/H7*Parameters!$B$5</f>
-        <v>16304.394</v>
+        <v>16130.943</v>
       </c>
       <c r="N7" s="11" t="n">
         <f aca="false">D7*E7*J7*Parameters!$B$4*I7/H7*Parameters!$B$5</f>
-        <v>5465.16</v>
+        <v>5407.02</v>
       </c>
       <c r="O7" s="11" t="n">
         <f aca="false">M7-M7*K7*L7</f>
-        <v>9415.787535</v>
+        <v>9315.6195825</v>
       </c>
       <c r="P7" s="12" t="n">
         <f aca="false">O7/N7</f>
@@ -24035,7 +24035,7 @@
       </c>
       <c r="J8" s="9" t="n">
         <f aca="false">Inputs!J11</f>
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="K8" s="12" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K11-C8))</f>
@@ -24047,15 +24047,15 @@
       </c>
       <c r="M8" s="11" t="n">
         <f aca="false">D8*E8*J8*((F8+G8)/2)*I8/H8*Parameters!$B$5</f>
-        <v>4495.96875</v>
+        <v>4447.625</v>
       </c>
       <c r="N8" s="11" t="n">
         <f aca="false">D8*E8*J8*Parameters!$B$4*I8/H8*Parameters!$B$5</f>
-        <v>2075.0625</v>
+        <v>2052.75</v>
       </c>
       <c r="O8" s="11" t="n">
         <f aca="false">M8-M8*K8*L8</f>
-        <v>1258.87125</v>
+        <v>1245.335</v>
       </c>
       <c r="P8" s="12" t="n">
         <f aca="false">O8/N8</f>
@@ -24103,7 +24103,7 @@
       </c>
       <c r="J9" s="9" t="n">
         <f aca="false">Inputs!J11</f>
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="K9" s="12" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K11-C9))</f>
@@ -24115,15 +24115,15 @@
       </c>
       <c r="M9" s="11" t="n">
         <f aca="false">D9*E9*J9*((F9+G9)/2)*I9/H9*Parameters!$B$5</f>
-        <v>9486</v>
+        <v>9384</v>
       </c>
       <c r="N9" s="11" t="n">
         <f aca="false">D9*E9*J9*Parameters!$B$4*I9/H9*Parameters!$B$5</f>
-        <v>3794.4</v>
+        <v>3753.6</v>
       </c>
       <c r="O9" s="11" t="n">
         <f aca="false">M9-M9*K9*L9</f>
-        <v>4173.84</v>
+        <v>4128.96</v>
       </c>
       <c r="P9" s="12" t="n">
         <f aca="false">O9/N9</f>
@@ -24171,7 +24171,7 @@
       </c>
       <c r="J10" s="9" t="n">
         <f aca="false">Inputs!J11</f>
-        <v>9.3</v>
+        <v>9.2</v>
       </c>
       <c r="K10" s="12" t="n">
         <f aca="false">MAX(0.05,MIN(0.99,Inputs!K11-C10))</f>
@@ -24183,15 +24183,15 @@
       </c>
       <c r="M10" s="11" t="n">
         <f aca="false">D10*E10*J10*((F10+G10)/2)*I10/H10*Parameters!$B$5</f>
-        <v>21041.13375</v>
+        <v>20814.885</v>
       </c>
       <c r="N10" s="11" t="n">
         <f aca="false">D10*E10*J10*Parameters!$B$4*I10/H10*Parameters!$B$5</f>
-        <v>7470.225</v>
+        <v>7389.9</v>
       </c>
       <c r="O10" s="11" t="n">
         <f aca="false">M10-M10*K10*L10</f>
-        <v>12203.857575</v>
+        <v>12072.6333</v>
       </c>
       <c r="P10" s="12" t="n">
         <f aca="false">O10/N10</f>
@@ -27785,7 +27785,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
         <v>84</v>
       </c>
@@ -28013,7 +28013,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
         <v>102</v>
       </c>
